--- a/distribucion/excel_analisis_datos/codigos/c10_proyecto/clientes.xlsx
+++ b/distribucion/excel_analisis_datos/codigos/c10_proyecto/clientes.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Básico</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>53</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -505,16 +505,16 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Básico</t>
+          <t>VIP</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Cusco</t>
+          <t>Lima</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4">
@@ -533,11 +533,11 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Trujillo</t>
+          <t>Arequipa</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5">
@@ -556,11 +556,11 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Arequipa</t>
+          <t>Piura</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -579,11 +579,11 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Trujillo</t>
+          <t>Cusco</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -597,16 +597,16 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>Básico</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Lima</t>
+          <t>Cusco</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>19</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8">
@@ -625,11 +625,11 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Cusco</t>
+          <t>Piura</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>19</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9">
@@ -643,16 +643,16 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Básico</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Arequipa</t>
+          <t>Piura</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>12</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10">
@@ -666,16 +666,16 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>VIP</t>
+          <t>Básico</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Trujillo</t>
+          <t>Lima</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11">
@@ -689,16 +689,16 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>VIP</t>
+          <t>Básico</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Cusco</t>
+          <t>Arequipa</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
